--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -2922,10 +2922,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119719028</v>
+        <v>119719023</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2934,25 +2934,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752873</v>
+        <v>752859</v>
       </c>
       <c r="R20" t="n">
-        <v>7096242</v>
+        <v>7096271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119718993</v>
+        <v>119718989</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3036,25 +3036,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752872</v>
+        <v>752861</v>
       </c>
       <c r="R21" t="n">
-        <v>7096313</v>
+        <v>7096410</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119719025</v>
+        <v>119719026</v>
       </c>
       <c r="B22" t="n">
         <v>91840</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119719027</v>
+        <v>119719028</v>
       </c>
       <c r="B23" t="n">
         <v>91840</v>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752872</v>
+        <v>752873</v>
       </c>
       <c r="R23" t="n">
-        <v>7096313</v>
+        <v>7096242</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119719023</v>
+        <v>119719029</v>
       </c>
       <c r="B24" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3342,25 +3342,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752859</v>
+        <v>752841</v>
       </c>
       <c r="R24" t="n">
-        <v>7096271</v>
+        <v>7096319</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119719029</v>
+        <v>119718993</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3444,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752841</v>
+        <v>752872</v>
       </c>
       <c r="R25" t="n">
-        <v>7096319</v>
+        <v>7096313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119718989</v>
+        <v>119719027</v>
       </c>
       <c r="B26" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3546,25 +3546,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752861</v>
+        <v>752872</v>
       </c>
       <c r="R26" t="n">
-        <v>7096410</v>
+        <v>7096313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -2922,10 +2922,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119719023</v>
+        <v>119718993</v>
       </c>
       <c r="B20" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2934,25 +2934,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752859</v>
+        <v>752872</v>
       </c>
       <c r="R20" t="n">
-        <v>7096271</v>
+        <v>7096313</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119718989</v>
+        <v>119719025</v>
       </c>
       <c r="B21" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3036,25 +3036,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119719026</v>
+        <v>119719027</v>
       </c>
       <c r="B22" t="n">
         <v>91840</v>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752861</v>
+        <v>752872</v>
       </c>
       <c r="R22" t="n">
-        <v>7096410</v>
+        <v>7096313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119719028</v>
+        <v>119719023</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3240,25 +3240,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752873</v>
+        <v>752859</v>
       </c>
       <c r="R23" t="n">
-        <v>7096242</v>
+        <v>7096271</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119719029</v>
+        <v>119718989</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3342,25 +3342,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752841</v>
+        <v>752861</v>
       </c>
       <c r="R24" t="n">
-        <v>7096319</v>
+        <v>7096410</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119718993</v>
+        <v>119719029</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3444,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752872</v>
+        <v>752841</v>
       </c>
       <c r="R25" t="n">
-        <v>7096313</v>
+        <v>7096319</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119719027</v>
+        <v>119719028</v>
       </c>
       <c r="B26" t="n">
         <v>91840</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752872</v>
+        <v>752873</v>
       </c>
       <c r="R26" t="n">
-        <v>7096313</v>
+        <v>7096242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3024,7 +3024,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119719025</v>
+        <v>119719027</v>
       </c>
       <c r="B21" t="n">
         <v>91840</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752861</v>
+        <v>752872</v>
       </c>
       <c r="R21" t="n">
-        <v>7096410</v>
+        <v>7096313</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119719027</v>
+        <v>119719025</v>
       </c>
       <c r="B22" t="n">
         <v>91840</v>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752872</v>
+        <v>752861</v>
       </c>
       <c r="R22" t="n">
-        <v>7096313</v>
+        <v>7096410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119718989</v>
+        <v>119719029</v>
       </c>
       <c r="B24" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3342,25 +3342,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752861</v>
+        <v>752841</v>
       </c>
       <c r="R24" t="n">
-        <v>7096410</v>
+        <v>7096319</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119719029</v>
+        <v>119719028</v>
       </c>
       <c r="B25" t="n">
         <v>91840</v>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752841</v>
+        <v>752873</v>
       </c>
       <c r="R25" t="n">
-        <v>7096319</v>
+        <v>7096242</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119719028</v>
+        <v>119718989</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3546,25 +3546,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752873</v>
+        <v>752861</v>
       </c>
       <c r="R26" t="n">
-        <v>7096242</v>
+        <v>7096410</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119719028</v>
+        <v>119718989</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3444,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752873</v>
+        <v>752861</v>
       </c>
       <c r="R25" t="n">
-        <v>7096242</v>
+        <v>7096410</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119718989</v>
+        <v>119719028</v>
       </c>
       <c r="B26" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3546,25 +3546,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752861</v>
+        <v>752873</v>
       </c>
       <c r="R26" t="n">
-        <v>7096410</v>
+        <v>7096242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119718989</v>
+        <v>119719028</v>
       </c>
       <c r="B25" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3444,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752861</v>
+        <v>752873</v>
       </c>
       <c r="R25" t="n">
-        <v>7096410</v>
+        <v>7096242</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119719028</v>
+        <v>119718989</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3546,25 +3546,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752873</v>
+        <v>752861</v>
       </c>
       <c r="R26" t="n">
-        <v>7096242</v>
+        <v>7096410</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -2925,7 +2925,7 @@
         <v>119718993</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119719027</v>
+        <v>119719025</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752872</v>
+        <v>752861</v>
       </c>
       <c r="R21" t="n">
-        <v>7096313</v>
+        <v>7096410</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,10 +3126,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119719025</v>
+        <v>119719029</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752861</v>
+        <v>752841</v>
       </c>
       <c r="R22" t="n">
-        <v>7096410</v>
+        <v>7096319</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119719023</v>
+        <v>119719028</v>
       </c>
       <c r="B23" t="n">
-        <v>89252</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3240,25 +3240,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752859</v>
+        <v>752873</v>
       </c>
       <c r="R23" t="n">
-        <v>7096271</v>
+        <v>7096242</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119719029</v>
+        <v>119719027</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752841</v>
+        <v>752872</v>
       </c>
       <c r="R24" t="n">
-        <v>7096319</v>
+        <v>7096313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119719028</v>
+        <v>119718989</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>89292</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3444,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752873</v>
+        <v>752861</v>
       </c>
       <c r="R25" t="n">
-        <v>7096242</v>
+        <v>7096410</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119718989</v>
+        <v>119719023</v>
       </c>
       <c r="B26" t="n">
-        <v>89275</v>
+        <v>89269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3550,21 +3550,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752861</v>
+        <v>752859</v>
       </c>
       <c r="R26" t="n">
-        <v>7096410</v>
+        <v>7096271</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3634,6 +3634,3293 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120382045</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>752897</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7096388</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120380690</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>752855</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7096096</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120381968</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>752894</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7096354</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120379894</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>752841</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7096393</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120381720</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>752888</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7096340</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120381175</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>752840</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7096209</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120381039</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>752854</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7096154</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120380082</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>752824</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7096268</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120380249</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>752872</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7096227</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120382031</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91874</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>752880</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7096382</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120380981</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>752849</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7096158</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe tunn</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120380698</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>752855</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7096096</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120381218</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>752828</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7096213</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120380394</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>752866</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7096140</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120379986</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91874</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>752810</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7096318</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120380784</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>752864</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7096134</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120380566</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>752866</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7096140</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120380429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>752866</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7096140</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120380299</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>752874</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7096153</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120380955</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>752864</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7096134</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120381495</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>752822</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7096246</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120380287</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>752880</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7096182</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120380070</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>752828</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7096259</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120379979</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>752829</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7096331</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120381406</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>752823</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7096244</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120382019</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>752883</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7096380</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120379906</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>752841</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7096393</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120380745</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>752848</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7096115</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120382173</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>752897</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7096388</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Växte dolt under fallen tallgren</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3636,7 +3636,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120382045</v>
+        <v>120379979</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752897</v>
+        <v>752829</v>
       </c>
       <c r="R27" t="n">
-        <v>7096388</v>
+        <v>7096331</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120380690</v>
+        <v>120380745</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3760,25 +3760,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752855</v>
+        <v>752848</v>
       </c>
       <c r="R28" t="n">
-        <v>7096096</v>
+        <v>7096115</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,7 +3860,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120381968</v>
+        <v>120380955</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752894</v>
+        <v>752864</v>
       </c>
       <c r="R29" t="n">
-        <v>7096354</v>
+        <v>7096134</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,10 +3972,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120379894</v>
+        <v>120380784</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3984,25 +3984,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752841</v>
+        <v>752864</v>
       </c>
       <c r="R30" t="n">
-        <v>7096393</v>
+        <v>7096134</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,7 +4057,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4084,10 +4089,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120381720</v>
+        <v>120380429</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4096,25 +4101,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4124,10 +4129,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752888</v>
+        <v>752866</v>
       </c>
       <c r="R31" t="n">
-        <v>7096340</v>
+        <v>7096140</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4159,7 +4164,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4169,7 +4174,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4196,10 +4201,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120381175</v>
+        <v>120380566</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>91881</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4208,46 +4213,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752840</v>
+        <v>752866</v>
       </c>
       <c r="R32" t="n">
-        <v>7096209</v>
+        <v>7096140</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120381039</v>
+        <v>120381495</v>
       </c>
       <c r="B33" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4325,25 +4325,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752854</v>
+        <v>752822</v>
       </c>
       <c r="R33" t="n">
-        <v>7096154</v>
+        <v>7096246</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4425,10 +4425,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120380082</v>
+        <v>120381175</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>57689</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4441,37 +4441,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752824</v>
+        <v>752840</v>
       </c>
       <c r="R34" t="n">
-        <v>7096268</v>
+        <v>7096209</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4500,7 +4505,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4510,7 +4515,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4537,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120380249</v>
+        <v>120380698</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4549,25 +4554,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4577,10 +4582,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752872</v>
+        <v>752855</v>
       </c>
       <c r="R35" t="n">
-        <v>7096227</v>
+        <v>7096096</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4612,7 +4617,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4622,7 +4627,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4649,10 +4654,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120382031</v>
+        <v>120380981</v>
       </c>
       <c r="B36" t="n">
-        <v>91874</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4665,37 +4670,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752880</v>
+        <v>752849</v>
       </c>
       <c r="R36" t="n">
-        <v>7096382</v>
+        <v>7096158</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4724,7 +4734,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4734,7 +4744,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe tunn</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4761,10 +4776,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120380981</v>
+        <v>120380394</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,46 +4788,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752849</v>
+        <v>752866</v>
       </c>
       <c r="R37" t="n">
-        <v>7096158</v>
+        <v>7096140</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4841,7 +4851,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4851,12 +4861,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe tunn</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4883,10 +4888,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120380698</v>
+        <v>120381218</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4899,21 +4904,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4923,10 +4928,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752855</v>
+        <v>752828</v>
       </c>
       <c r="R38" t="n">
-        <v>7096096</v>
+        <v>7096213</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4958,7 +4963,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4968,7 +4973,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4995,10 +5000,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120381218</v>
+        <v>120381039</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5011,21 +5016,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752828</v>
+        <v>752854</v>
       </c>
       <c r="R39" t="n">
-        <v>7096213</v>
+        <v>7096154</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5070,7 +5075,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5080,7 +5085,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5107,10 +5112,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120380394</v>
+        <v>120382173</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5119,25 +5124,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5147,13 +5152,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>752866</v>
+        <v>752897</v>
       </c>
       <c r="R40" t="n">
-        <v>7096140</v>
+        <v>7096388</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5192,7 +5197,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Växte dolt under fallen tallgren</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5219,10 +5229,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120379986</v>
+        <v>120382086</v>
       </c>
       <c r="B41" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5231,25 +5241,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5259,13 +5269,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752810</v>
+        <v>752897</v>
       </c>
       <c r="R41" t="n">
-        <v>7096318</v>
+        <v>7096388</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5294,7 +5304,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5304,7 +5314,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,10 +5341,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120380784</v>
+        <v>120381720</v>
       </c>
       <c r="B42" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5343,25 +5353,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752864</v>
+        <v>752888</v>
       </c>
       <c r="R42" t="n">
-        <v>7096134</v>
+        <v>7096340</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5406,7 +5416,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5416,12 +5426,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5448,10 +5453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120380566</v>
+        <v>120382019</v>
       </c>
       <c r="B43" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5460,25 +5465,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5488,13 +5493,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752866</v>
+        <v>752883</v>
       </c>
       <c r="R43" t="n">
-        <v>7096140</v>
+        <v>7096380</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5523,7 +5528,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5533,7 +5538,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5560,10 +5565,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120380429</v>
+        <v>120381956</v>
       </c>
       <c r="B44" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5572,25 +5577,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5600,13 +5605,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752866</v>
+        <v>752894</v>
       </c>
       <c r="R44" t="n">
-        <v>7096140</v>
+        <v>7096354</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5635,7 +5640,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5645,7 +5650,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5672,10 +5677,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120380299</v>
+        <v>120379906</v>
       </c>
       <c r="B45" t="n">
-        <v>91852</v>
+        <v>57336</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5688,34 +5693,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752874</v>
+        <v>752841</v>
       </c>
       <c r="R45" t="n">
-        <v>7096153</v>
+        <v>7096393</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5747,7 +5757,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5757,7 +5767,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5784,7 +5794,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120380955</v>
+        <v>120380082</v>
       </c>
       <c r="B46" t="n">
         <v>91858</v>
@@ -5824,10 +5834,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752864</v>
+        <v>752824</v>
       </c>
       <c r="R46" t="n">
-        <v>7096134</v>
+        <v>7096268</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5859,7 +5869,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5869,7 +5879,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5896,10 +5906,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120381495</v>
+        <v>120380287</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5908,25 +5918,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5936,13 +5946,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752822</v>
+        <v>752880</v>
       </c>
       <c r="R47" t="n">
-        <v>7096246</v>
+        <v>7096182</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5971,7 +5981,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5981,7 +5991,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6008,10 +6018,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120380287</v>
+        <v>120380690</v>
       </c>
       <c r="B48" t="n">
-        <v>91850</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6024,21 +6034,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6048,13 +6058,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752880</v>
+        <v>752855</v>
       </c>
       <c r="R48" t="n">
-        <v>7096182</v>
+        <v>7096096</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6083,7 +6093,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6093,7 +6103,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6232,10 +6242,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120379979</v>
+        <v>120380299</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6244,25 +6254,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6272,10 +6282,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752829</v>
+        <v>752874</v>
       </c>
       <c r="R50" t="n">
-        <v>7096331</v>
+        <v>7096153</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6307,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6317,7 +6327,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6344,10 +6354,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120381406</v>
+        <v>120379986</v>
       </c>
       <c r="B51" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6360,46 +6370,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>752823</v>
+        <v>752810</v>
       </c>
       <c r="R51" t="n">
-        <v>7096244</v>
+        <v>7096318</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6428,7 +6429,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6438,7 +6439,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6465,7 +6466,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120382019</v>
+        <v>120379894</v>
       </c>
       <c r="B52" t="n">
         <v>91858</v>
@@ -6505,13 +6506,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752883</v>
+        <v>752841</v>
       </c>
       <c r="R52" t="n">
-        <v>7096380</v>
+        <v>7096393</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6540,7 +6541,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6550,7 +6551,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6577,10 +6578,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120379906</v>
+        <v>120381406</v>
       </c>
       <c r="B53" t="n">
-        <v>57336</v>
+        <v>91850</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6593,42 +6594,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Hissjö, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752841</v>
+        <v>752823</v>
       </c>
       <c r="R53" t="n">
-        <v>7096393</v>
+        <v>7096244</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6657,7 +6662,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6667,7 +6672,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6694,10 +6699,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120380745</v>
+        <v>120382031</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6706,25 +6711,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6734,13 +6739,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752848</v>
+        <v>752880</v>
       </c>
       <c r="R54" t="n">
-        <v>7096115</v>
+        <v>7096382</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6769,7 +6774,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6779,7 +6784,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6806,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120382173</v>
+        <v>120380249</v>
       </c>
       <c r="B55" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6818,25 +6823,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6846,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752897</v>
+        <v>752872</v>
       </c>
       <c r="R55" t="n">
-        <v>7096388</v>
+        <v>7096227</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6881,7 +6886,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6891,12 +6896,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Växte dolt under fallen tallgren</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3636,7 +3636,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120379979</v>
+        <v>120380745</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752829</v>
+        <v>752848</v>
       </c>
       <c r="R27" t="n">
-        <v>7096331</v>
+        <v>7096115</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120380745</v>
+        <v>120379986</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3760,25 +3760,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752848</v>
+        <v>752810</v>
       </c>
       <c r="R28" t="n">
-        <v>7096115</v>
+        <v>7096318</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120380955</v>
+        <v>120380698</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,25 +3872,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752864</v>
+        <v>752855</v>
       </c>
       <c r="R29" t="n">
-        <v>7096134</v>
+        <v>7096096</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,10 +3972,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120380784</v>
+        <v>120381039</v>
       </c>
       <c r="B30" t="n">
-        <v>91862</v>
+        <v>91852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3984,25 +3984,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752864</v>
+        <v>752854</v>
       </c>
       <c r="R30" t="n">
-        <v>7096134</v>
+        <v>7096154</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,12 +4057,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4089,10 +4084,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120380429</v>
+        <v>120382019</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4101,25 +4096,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4129,13 +4124,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752866</v>
+        <v>752883</v>
       </c>
       <c r="R31" t="n">
-        <v>7096140</v>
+        <v>7096380</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4164,7 +4159,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4174,7 +4169,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4201,10 +4196,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120380566</v>
+        <v>120381218</v>
       </c>
       <c r="B32" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4217,21 +4212,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4241,10 +4236,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752866</v>
+        <v>752828</v>
       </c>
       <c r="R32" t="n">
-        <v>7096140</v>
+        <v>7096213</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4276,7 +4271,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,7 +4281,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4313,7 +4308,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120381495</v>
+        <v>120380070</v>
       </c>
       <c r="B33" t="n">
         <v>91858</v>
@@ -4353,10 +4348,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752822</v>
+        <v>752828</v>
       </c>
       <c r="R33" t="n">
-        <v>7096246</v>
+        <v>7096259</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4388,7 +4383,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4398,7 +4393,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4425,10 +4420,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120381175</v>
+        <v>120381495</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4441,42 +4436,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752840</v>
+        <v>752822</v>
       </c>
       <c r="R34" t="n">
-        <v>7096209</v>
+        <v>7096246</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4505,7 +4495,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4515,7 +4505,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4542,10 +4532,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120380698</v>
+        <v>120380784</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,25 +4544,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4582,10 +4572,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752855</v>
+        <v>752864</v>
       </c>
       <c r="R35" t="n">
-        <v>7096096</v>
+        <v>7096134</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4617,7 +4607,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4627,7 +4617,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4654,10 +4649,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120380981</v>
+        <v>120380429</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>91852</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4670,39 +4665,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752849</v>
+        <v>752866</v>
       </c>
       <c r="R36" t="n">
-        <v>7096158</v>
+        <v>7096140</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4734,7 +4724,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4744,12 +4734,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe tunn</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4776,7 +4761,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120380394</v>
+        <v>120380249</v>
       </c>
       <c r="B37" t="n">
         <v>91858</v>
@@ -4816,13 +4801,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752866</v>
+        <v>752872</v>
       </c>
       <c r="R37" t="n">
-        <v>7096140</v>
+        <v>7096227</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4851,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4861,7 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4888,10 +4873,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120381218</v>
+        <v>120380690</v>
       </c>
       <c r="B38" t="n">
-        <v>91850</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4904,21 +4889,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4928,10 +4913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752828</v>
+        <v>752855</v>
       </c>
       <c r="R38" t="n">
-        <v>7096213</v>
+        <v>7096096</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4963,7 +4948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4973,7 +4958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5000,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120381039</v>
+        <v>120380132</v>
       </c>
       <c r="B39" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5012,25 +4997,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5040,10 +5025,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752854</v>
+        <v>752824</v>
       </c>
       <c r="R39" t="n">
-        <v>7096154</v>
+        <v>7096268</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5075,7 +5060,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5085,7 +5070,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5112,10 +5097,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120382173</v>
+        <v>120379979</v>
       </c>
       <c r="B40" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5124,25 +5109,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5152,10 +5137,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>752897</v>
+        <v>752829</v>
       </c>
       <c r="R40" t="n">
-        <v>7096388</v>
+        <v>7096331</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5187,7 +5172,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5197,12 +5182,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växte dolt under fallen tallgren</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5229,7 +5209,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120382086</v>
+        <v>120380394</v>
       </c>
       <c r="B41" t="n">
         <v>91858</v>
@@ -5269,10 +5249,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752897</v>
+        <v>752866</v>
       </c>
       <c r="R41" t="n">
-        <v>7096388</v>
+        <v>7096140</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5304,7 +5284,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5314,7 +5294,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5341,10 +5321,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120381720</v>
+        <v>120380299</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5353,25 +5333,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5381,10 +5361,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752888</v>
+        <v>752874</v>
       </c>
       <c r="R42" t="n">
-        <v>7096340</v>
+        <v>7096153</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5416,7 +5396,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5426,7 +5406,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5453,7 +5433,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120382019</v>
+        <v>120381956</v>
       </c>
       <c r="B43" t="n">
         <v>91858</v>
@@ -5493,10 +5473,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752883</v>
+        <v>752894</v>
       </c>
       <c r="R43" t="n">
-        <v>7096380</v>
+        <v>7096354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5528,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5538,7 +5518,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5565,7 +5545,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120381956</v>
+        <v>120381720</v>
       </c>
       <c r="B44" t="n">
         <v>91858</v>
@@ -5605,13 +5585,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752894</v>
+        <v>752888</v>
       </c>
       <c r="R44" t="n">
-        <v>7096354</v>
+        <v>7096340</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5640,7 +5620,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5650,7 +5630,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5677,10 +5657,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120379906</v>
+        <v>120382031</v>
       </c>
       <c r="B45" t="n">
-        <v>57336</v>
+        <v>91874</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5693,42 +5673,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Hissjö, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752841</v>
+        <v>752880</v>
       </c>
       <c r="R45" t="n">
-        <v>7096393</v>
+        <v>7096382</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5757,7 +5732,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5767,7 +5742,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5794,10 +5769,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120380082</v>
+        <v>120380287</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5806,25 +5781,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5834,13 +5809,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752824</v>
+        <v>752880</v>
       </c>
       <c r="R46" t="n">
-        <v>7096268</v>
+        <v>7096182</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5869,7 +5844,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5879,7 +5854,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5906,10 +5881,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120380287</v>
+        <v>120380981</v>
       </c>
       <c r="B47" t="n">
-        <v>91850</v>
+        <v>57336</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5922,37 +5897,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752880</v>
+        <v>752849</v>
       </c>
       <c r="R47" t="n">
-        <v>7096182</v>
+        <v>7096158</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5981,7 +5961,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5991,7 +5971,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe tunn</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6018,10 +6003,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120380690</v>
+        <v>120379894</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6030,25 +6015,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6058,10 +6043,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752855</v>
+        <v>752841</v>
       </c>
       <c r="R48" t="n">
-        <v>7096096</v>
+        <v>7096393</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6093,7 +6078,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6103,7 +6088,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6130,10 +6115,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120380070</v>
+        <v>120379906</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6142,38 +6127,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752828</v>
+        <v>752841</v>
       </c>
       <c r="R49" t="n">
-        <v>7096259</v>
+        <v>7096393</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6205,7 +6195,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6215,7 +6205,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6242,10 +6232,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120380299</v>
+        <v>120380566</v>
       </c>
       <c r="B50" t="n">
-        <v>91852</v>
+        <v>91881</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6258,21 +6248,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6282,10 +6272,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752874</v>
+        <v>752866</v>
       </c>
       <c r="R50" t="n">
-        <v>7096153</v>
+        <v>7096140</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6317,7 +6307,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6317,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6354,10 +6344,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120379986</v>
+        <v>120382173</v>
       </c>
       <c r="B51" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6370,21 +6360,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6394,10 +6384,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>752810</v>
+        <v>752897</v>
       </c>
       <c r="R51" t="n">
-        <v>7096318</v>
+        <v>7096388</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6429,7 +6419,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6439,7 +6429,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Växte dolt under fallen tallgren</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6466,7 +6461,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120379894</v>
+        <v>120382086</v>
       </c>
       <c r="B52" t="n">
         <v>91858</v>
@@ -6506,13 +6501,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752841</v>
+        <v>752897</v>
       </c>
       <c r="R52" t="n">
-        <v>7096393</v>
+        <v>7096388</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6541,7 +6536,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6551,7 +6546,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6699,10 +6694,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120382031</v>
+        <v>120381175</v>
       </c>
       <c r="B54" t="n">
-        <v>91874</v>
+        <v>57689</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6711,38 +6706,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752880</v>
+        <v>752840</v>
       </c>
       <c r="R54" t="n">
-        <v>7096382</v>
+        <v>7096209</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6811,7 +6811,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120380249</v>
+        <v>120380955</v>
       </c>
       <c r="B55" t="n">
         <v>91858</v>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752872</v>
+        <v>752864</v>
       </c>
       <c r="R55" t="n">
-        <v>7096227</v>
+        <v>7096134</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3636,7 +3636,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120380745</v>
+        <v>120379894</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752848</v>
+        <v>752841</v>
       </c>
       <c r="R27" t="n">
-        <v>7096115</v>
+        <v>7096393</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120379986</v>
+        <v>120380429</v>
       </c>
       <c r="B28" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752810</v>
+        <v>752866</v>
       </c>
       <c r="R28" t="n">
-        <v>7096318</v>
+        <v>7096140</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120380698</v>
+        <v>120382031</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3876,21 +3876,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752855</v>
+        <v>752880</v>
       </c>
       <c r="R29" t="n">
-        <v>7096096</v>
+        <v>7096382</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,10 +3972,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120381039</v>
+        <v>120380566</v>
       </c>
       <c r="B30" t="n">
-        <v>91852</v>
+        <v>91881</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3988,21 +3988,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752854</v>
+        <v>752866</v>
       </c>
       <c r="R30" t="n">
-        <v>7096154</v>
+        <v>7096140</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4084,7 +4084,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120382019</v>
+        <v>120381495</v>
       </c>
       <c r="B31" t="n">
         <v>91858</v>
@@ -4124,13 +4124,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752883</v>
+        <v>752822</v>
       </c>
       <c r="R31" t="n">
-        <v>7096380</v>
+        <v>7096246</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120381218</v>
+        <v>120380070</v>
       </c>
       <c r="B32" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4208,25 +4208,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>752828</v>
       </c>
       <c r="R32" t="n">
-        <v>7096213</v>
+        <v>7096259</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120380070</v>
+        <v>120380981</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4320,38 +4320,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752828</v>
+        <v>752849</v>
       </c>
       <c r="R33" t="n">
-        <v>7096259</v>
+        <v>7096158</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4383,7 +4388,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4393,7 +4398,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe tunn</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4420,7 +4430,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120381495</v>
+        <v>120380132</v>
       </c>
       <c r="B34" t="n">
         <v>91858</v>
@@ -4460,10 +4470,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752822</v>
+        <v>752824</v>
       </c>
       <c r="R34" t="n">
-        <v>7096246</v>
+        <v>7096268</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4495,7 +4505,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4505,7 +4515,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4532,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120380784</v>
+        <v>120382086</v>
       </c>
       <c r="B35" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4544,25 +4554,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4572,13 +4582,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752864</v>
+        <v>752897</v>
       </c>
       <c r="R35" t="n">
-        <v>7096134</v>
+        <v>7096388</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4607,7 +4617,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4617,12 +4627,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4649,10 +4654,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120380429</v>
+        <v>120380745</v>
       </c>
       <c r="B36" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4661,25 +4666,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4689,10 +4694,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752866</v>
+        <v>752848</v>
       </c>
       <c r="R36" t="n">
-        <v>7096140</v>
+        <v>7096115</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4724,7 +4729,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4734,7 +4739,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4761,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120380249</v>
+        <v>120381218</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4801,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752872</v>
+        <v>752828</v>
       </c>
       <c r="R37" t="n">
-        <v>7096227</v>
+        <v>7096213</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4836,7 +4841,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4846,7 +4851,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4873,10 +4878,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120380690</v>
+        <v>120379979</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4885,25 +4890,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4913,10 +4918,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752855</v>
+        <v>752829</v>
       </c>
       <c r="R38" t="n">
-        <v>7096096</v>
+        <v>7096331</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4948,7 +4953,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4958,7 +4963,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4985,10 +4990,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120380132</v>
+        <v>120380299</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4997,25 +5002,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5025,10 +5030,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752824</v>
+        <v>752874</v>
       </c>
       <c r="R39" t="n">
-        <v>7096268</v>
+        <v>7096153</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5060,7 +5065,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5070,7 +5075,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5097,10 +5102,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120379979</v>
+        <v>120380784</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5109,25 +5114,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5137,10 +5142,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>752829</v>
+        <v>752864</v>
       </c>
       <c r="R40" t="n">
-        <v>7096331</v>
+        <v>7096134</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5172,7 +5177,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5182,7 +5187,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5209,10 +5219,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120380394</v>
+        <v>120379986</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5221,25 +5231,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5249,13 +5259,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752866</v>
+        <v>752810</v>
       </c>
       <c r="R41" t="n">
-        <v>7096140</v>
+        <v>7096318</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5284,7 +5294,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5294,7 +5304,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5321,10 +5331,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120380299</v>
+        <v>120381175</v>
       </c>
       <c r="B42" t="n">
-        <v>91852</v>
+        <v>57689</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5333,41 +5343,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752874</v>
+        <v>752840</v>
       </c>
       <c r="R42" t="n">
-        <v>7096153</v>
+        <v>7096209</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5396,7 +5411,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5406,7 +5421,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,10 +5448,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120381956</v>
+        <v>120380287</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5445,25 +5460,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5473,10 +5488,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752894</v>
+        <v>752880</v>
       </c>
       <c r="R43" t="n">
-        <v>7096354</v>
+        <v>7096182</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5508,7 +5523,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5518,7 +5533,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5545,7 +5560,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120381720</v>
+        <v>120380394</v>
       </c>
       <c r="B44" t="n">
         <v>91858</v>
@@ -5585,13 +5600,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752888</v>
+        <v>752866</v>
       </c>
       <c r="R44" t="n">
-        <v>7096340</v>
+        <v>7096140</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5620,7 +5635,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5630,7 +5645,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5657,10 +5672,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120382031</v>
+        <v>120381406</v>
       </c>
       <c r="B45" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5673,34 +5688,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752880</v>
+        <v>752823</v>
       </c>
       <c r="R45" t="n">
-        <v>7096382</v>
+        <v>7096244</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5732,7 +5756,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5742,7 +5766,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5769,10 +5793,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120380287</v>
+        <v>120381968</v>
       </c>
       <c r="B46" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5781,25 +5805,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5809,10 +5833,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752880</v>
+        <v>752894</v>
       </c>
       <c r="R46" t="n">
-        <v>7096182</v>
+        <v>7096354</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5844,7 +5868,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5854,7 +5878,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5881,10 +5905,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120380981</v>
+        <v>120382173</v>
       </c>
       <c r="B47" t="n">
-        <v>57336</v>
+        <v>91901</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5897,39 +5921,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>5448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752849</v>
+        <v>752897</v>
       </c>
       <c r="R47" t="n">
-        <v>7096158</v>
+        <v>7096388</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5961,7 +5980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5971,12 +5990,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tallhögstubbe tunn</t>
+          <t>Växte dolt under fallen tallgren</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6003,10 +6022,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120379894</v>
+        <v>120380698</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6015,25 +6034,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6043,10 +6062,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752841</v>
+        <v>752855</v>
       </c>
       <c r="R48" t="n">
-        <v>7096393</v>
+        <v>7096096</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6078,7 +6097,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6088,7 +6107,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6115,10 +6134,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120379906</v>
+        <v>120380955</v>
       </c>
       <c r="B49" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6127,43 +6146,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Hissjö, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752841</v>
+        <v>752864</v>
       </c>
       <c r="R49" t="n">
-        <v>7096393</v>
+        <v>7096134</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6195,7 +6209,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6205,7 +6219,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6232,10 +6246,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120380566</v>
+        <v>120381039</v>
       </c>
       <c r="B50" t="n">
-        <v>91881</v>
+        <v>91852</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6248,21 +6262,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6272,10 +6286,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752866</v>
+        <v>752854</v>
       </c>
       <c r="R50" t="n">
-        <v>7096140</v>
+        <v>7096154</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6307,7 +6321,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6317,7 +6331,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6344,10 +6358,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120382173</v>
+        <v>120381720</v>
       </c>
       <c r="B51" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6356,25 +6370,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6384,10 +6398,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>752897</v>
+        <v>752888</v>
       </c>
       <c r="R51" t="n">
-        <v>7096388</v>
+        <v>7096340</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6419,7 +6433,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6429,12 +6443,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Växte dolt under fallen tallgren</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,7 +6470,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120382086</v>
+        <v>120380249</v>
       </c>
       <c r="B52" t="n">
         <v>91858</v>
@@ -6501,13 +6510,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752897</v>
+        <v>752872</v>
       </c>
       <c r="R52" t="n">
-        <v>7096388</v>
+        <v>7096227</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6536,7 +6545,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6546,7 +6555,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6573,10 +6582,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120381406</v>
+        <v>120379906</v>
       </c>
       <c r="B53" t="n">
-        <v>91850</v>
+        <v>57336</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6589,46 +6598,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752823</v>
+        <v>752841</v>
       </c>
       <c r="R53" t="n">
-        <v>7096244</v>
+        <v>7096393</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6657,7 +6662,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6667,7 +6672,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6694,10 +6699,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120381175</v>
+        <v>120382019</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6710,39 +6715,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752840</v>
+        <v>752883</v>
       </c>
       <c r="R54" t="n">
-        <v>7096209</v>
+        <v>7096380</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6811,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120380955</v>
+        <v>120380690</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6823,25 +6823,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752864</v>
+        <v>752855</v>
       </c>
       <c r="R55" t="n">
-        <v>7096134</v>
+        <v>7096096</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3636,7 +3636,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120379894</v>
+        <v>120382086</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752841</v>
+        <v>752897</v>
       </c>
       <c r="R27" t="n">
-        <v>7096393</v>
+        <v>7096388</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120380429</v>
+        <v>120380394</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3760,25 +3760,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
         <v>7096140</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120382031</v>
+        <v>120380981</v>
       </c>
       <c r="B29" t="n">
-        <v>91874</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3876,37 +3876,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752880</v>
+        <v>752849</v>
       </c>
       <c r="R29" t="n">
-        <v>7096382</v>
+        <v>7096158</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3950,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe tunn</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,10 +3982,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120380566</v>
+        <v>120379906</v>
       </c>
       <c r="B30" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3988,34 +3998,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752866</v>
+        <v>752841</v>
       </c>
       <c r="R30" t="n">
-        <v>7096140</v>
+        <v>7096393</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4047,7 +4062,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,7 +4072,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4084,10 +4099,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120381495</v>
+        <v>120380698</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4096,25 +4111,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4124,10 +4139,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752822</v>
+        <v>752855</v>
       </c>
       <c r="R31" t="n">
-        <v>7096246</v>
+        <v>7096096</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4159,7 +4174,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4169,7 +4184,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4196,10 +4211,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120380070</v>
+        <v>120380566</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4208,25 +4223,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4236,10 +4251,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752828</v>
+        <v>752866</v>
       </c>
       <c r="R32" t="n">
-        <v>7096259</v>
+        <v>7096140</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4271,7 +4286,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4281,7 +4296,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,10 +4323,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120380981</v>
+        <v>120380287</v>
       </c>
       <c r="B33" t="n">
-        <v>57336</v>
+        <v>91850</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4324,42 +4339,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752849</v>
+        <v>752880</v>
       </c>
       <c r="R33" t="n">
-        <v>7096158</v>
+        <v>7096182</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4388,7 +4398,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4398,12 +4408,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe tunn</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4430,7 +4435,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120380132</v>
+        <v>120379979</v>
       </c>
       <c r="B34" t="n">
         <v>91858</v>
@@ -4470,10 +4475,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752824</v>
+        <v>752829</v>
       </c>
       <c r="R34" t="n">
-        <v>7096268</v>
+        <v>7096331</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4505,7 +4510,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4515,7 +4520,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4542,10 +4547,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120382086</v>
+        <v>120381039</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,25 +4559,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4582,13 +4587,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752897</v>
+        <v>752854</v>
       </c>
       <c r="R35" t="n">
-        <v>7096388</v>
+        <v>7096154</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4617,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4627,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4654,10 +4659,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120380745</v>
+        <v>120380299</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4666,25 +4671,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4694,10 +4699,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752848</v>
+        <v>752874</v>
       </c>
       <c r="R36" t="n">
-        <v>7096115</v>
+        <v>7096153</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4729,7 +4734,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4739,7 +4744,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,10 +4771,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120381218</v>
+        <v>120380690</v>
       </c>
       <c r="B37" t="n">
-        <v>91850</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4782,21 +4787,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4811,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752828</v>
+        <v>752855</v>
       </c>
       <c r="R37" t="n">
-        <v>7096213</v>
+        <v>7096096</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4841,7 +4846,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4851,7 +4856,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4878,7 +4883,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120379979</v>
+        <v>120380955</v>
       </c>
       <c r="B38" t="n">
         <v>91858</v>
@@ -4918,10 +4923,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752829</v>
+        <v>752864</v>
       </c>
       <c r="R38" t="n">
-        <v>7096331</v>
+        <v>7096134</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4953,7 +4958,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4963,7 +4968,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4990,10 +4995,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120380299</v>
+        <v>120380082</v>
       </c>
       <c r="B39" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5002,25 +5007,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5030,10 +5035,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752874</v>
+        <v>752824</v>
       </c>
       <c r="R39" t="n">
-        <v>7096153</v>
+        <v>7096268</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5065,7 +5070,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5075,7 +5080,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5102,10 +5107,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120380784</v>
+        <v>120379894</v>
       </c>
       <c r="B40" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5114,25 +5119,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5142,10 +5147,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>752864</v>
+        <v>752841</v>
       </c>
       <c r="R40" t="n">
-        <v>7096134</v>
+        <v>7096393</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5177,7 +5182,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5187,12 +5192,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5219,7 +5219,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120379986</v>
+        <v>120382031</v>
       </c>
       <c r="B41" t="n">
         <v>91874</v>
@@ -5259,13 +5259,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752810</v>
+        <v>752880</v>
       </c>
       <c r="R41" t="n">
-        <v>7096318</v>
+        <v>7096382</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,10 +5331,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120381175</v>
+        <v>120381495</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5347,42 +5347,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752840</v>
+        <v>752822</v>
       </c>
       <c r="R42" t="n">
-        <v>7096209</v>
+        <v>7096246</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5411,7 +5406,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5421,7 +5416,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5448,10 +5443,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120380287</v>
+        <v>120382019</v>
       </c>
       <c r="B43" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5460,25 +5455,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5488,10 +5483,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752880</v>
+        <v>752883</v>
       </c>
       <c r="R43" t="n">
-        <v>7096182</v>
+        <v>7096380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5523,7 +5518,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5533,7 +5528,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5560,10 +5555,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120380394</v>
+        <v>120379986</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5572,25 +5567,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5600,13 +5595,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752866</v>
+        <v>752810</v>
       </c>
       <c r="R44" t="n">
-        <v>7096140</v>
+        <v>7096318</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5635,7 +5630,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5645,7 +5640,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5672,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120381406</v>
+        <v>120381720</v>
       </c>
       <c r="B45" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5684,50 +5679,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752823</v>
+        <v>752888</v>
       </c>
       <c r="R45" t="n">
-        <v>7096244</v>
+        <v>7096340</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5756,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5766,7 +5752,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5793,10 +5779,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120381968</v>
+        <v>120381175</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>57689</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5809,34 +5795,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752894</v>
+        <v>752840</v>
       </c>
       <c r="R46" t="n">
-        <v>7096354</v>
+        <v>7096209</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5868,7 +5859,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5878,7 +5869,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5905,10 +5896,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120382173</v>
+        <v>120380429</v>
       </c>
       <c r="B47" t="n">
-        <v>91901</v>
+        <v>91852</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5921,21 +5912,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5945,10 +5936,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752897</v>
+        <v>752866</v>
       </c>
       <c r="R47" t="n">
-        <v>7096388</v>
+        <v>7096140</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5980,7 +5971,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5990,12 +5981,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Växte dolt under fallen tallgren</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6022,10 +6008,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120380698</v>
+        <v>120380745</v>
       </c>
       <c r="B48" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6034,25 +6020,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6062,10 +6048,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752855</v>
+        <v>752848</v>
       </c>
       <c r="R48" t="n">
-        <v>7096096</v>
+        <v>7096115</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6097,7 +6083,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6107,7 +6093,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6134,10 +6120,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120380955</v>
+        <v>120382173</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6146,25 +6132,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6174,10 +6160,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752864</v>
+        <v>752897</v>
       </c>
       <c r="R49" t="n">
-        <v>7096134</v>
+        <v>7096388</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6209,7 +6195,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6219,7 +6205,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Växte dolt under fallen tallgren</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6246,10 +6237,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120381039</v>
+        <v>120380249</v>
       </c>
       <c r="B50" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6258,25 +6249,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6286,10 +6277,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752854</v>
+        <v>752872</v>
       </c>
       <c r="R50" t="n">
-        <v>7096154</v>
+        <v>7096227</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6321,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6331,7 +6322,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6358,7 +6349,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120381720</v>
+        <v>120381968</v>
       </c>
       <c r="B51" t="n">
         <v>91858</v>
@@ -6398,13 +6389,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>752888</v>
+        <v>752894</v>
       </c>
       <c r="R51" t="n">
-        <v>7096340</v>
+        <v>7096354</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6433,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6443,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6470,10 +6461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120380249</v>
+        <v>120381406</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6482,41 +6473,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752872</v>
+        <v>752823</v>
       </c>
       <c r="R52" t="n">
-        <v>7096227</v>
+        <v>7096244</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6582,10 +6582,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120379906</v>
+        <v>120380784</v>
       </c>
       <c r="B53" t="n">
-        <v>57336</v>
+        <v>91862</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6594,43 +6594,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Hissjö, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752841</v>
+        <v>752864</v>
       </c>
       <c r="R53" t="n">
-        <v>7096393</v>
+        <v>7096134</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6662,7 +6657,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6672,7 +6667,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6699,10 +6699,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120382019</v>
+        <v>120381218</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6711,25 +6711,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752883</v>
+        <v>752828</v>
       </c>
       <c r="R54" t="n">
-        <v>7096380</v>
+        <v>7096213</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6811,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120380690</v>
+        <v>120380070</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6823,25 +6823,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752855</v>
+        <v>752828</v>
       </c>
       <c r="R55" t="n">
-        <v>7096096</v>
+        <v>7096259</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -6461,7 +6461,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120381406</v>
+        <v>120381218</v>
       </c>
       <c r="B52" t="n">
         <v>91850</v>
@@ -6494,29 +6494,20 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752823</v>
+        <v>752828</v>
       </c>
       <c r="R52" t="n">
-        <v>7096244</v>
+        <v>7096213</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6545,7 +6536,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6555,7 +6546,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6582,10 +6573,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120380784</v>
+        <v>120381406</v>
       </c>
       <c r="B53" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6594,41 +6585,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752864</v>
+        <v>752823</v>
       </c>
       <c r="R53" t="n">
-        <v>7096134</v>
+        <v>7096244</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6667,12 +6667,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6699,10 +6694,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120381218</v>
+        <v>120380784</v>
       </c>
       <c r="B54" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6711,25 +6706,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6739,10 +6734,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752828</v>
+        <v>752864</v>
       </c>
       <c r="R54" t="n">
-        <v>7096213</v>
+        <v>7096134</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6774,7 +6769,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6784,7 +6779,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3636,10 +3636,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120382086</v>
+        <v>120379906</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3648,41 +3648,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752897</v>
+        <v>752841</v>
       </c>
       <c r="R27" t="n">
-        <v>7096388</v>
+        <v>7096393</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3711,7 +3716,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3726,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120380394</v>
+        <v>120379986</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3760,25 +3765,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3788,13 +3793,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752866</v>
+        <v>752810</v>
       </c>
       <c r="R28" t="n">
-        <v>7096140</v>
+        <v>7096318</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3823,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3838,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3865,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120380981</v>
+        <v>120380132</v>
       </c>
       <c r="B29" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,43 +3877,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752849</v>
+        <v>752824</v>
       </c>
       <c r="R29" t="n">
-        <v>7096158</v>
+        <v>7096268</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3950,12 +3950,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe tunn</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3982,10 +3977,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120379906</v>
+        <v>120380287</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>91850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3998,42 +3993,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Hissjö, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752841</v>
+        <v>752880</v>
       </c>
       <c r="R30" t="n">
-        <v>7096393</v>
+        <v>7096182</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4062,7 +4052,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4072,7 +4062,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,10 +4201,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120380566</v>
+        <v>120381720</v>
       </c>
       <c r="B32" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4223,25 +4213,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4251,10 +4241,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752866</v>
+        <v>752888</v>
       </c>
       <c r="R32" t="n">
-        <v>7096140</v>
+        <v>7096340</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4286,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4296,7 +4286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4323,10 +4313,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120380287</v>
+        <v>120381175</v>
       </c>
       <c r="B33" t="n">
-        <v>91850</v>
+        <v>57689</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4335,38 +4325,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752880</v>
+        <v>752840</v>
       </c>
       <c r="R33" t="n">
-        <v>7096182</v>
+        <v>7096209</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4435,10 +4430,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120379979</v>
+        <v>120380981</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4447,38 +4442,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752829</v>
+        <v>752849</v>
       </c>
       <c r="R34" t="n">
-        <v>7096331</v>
+        <v>7096158</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4520,7 +4520,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe tunn</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4547,10 +4552,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120381039</v>
+        <v>120380249</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4559,25 +4564,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4592,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752854</v>
+        <v>752872</v>
       </c>
       <c r="R35" t="n">
-        <v>7096154</v>
+        <v>7096227</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4622,7 +4627,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4637,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120380299</v>
+        <v>120379979</v>
       </c>
       <c r="B36" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4699,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752874</v>
+        <v>752829</v>
       </c>
       <c r="R36" t="n">
-        <v>7096153</v>
+        <v>7096331</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4734,7 +4739,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4771,10 +4776,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120380690</v>
+        <v>120380784</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>91862</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4783,25 +4788,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4811,10 +4816,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752855</v>
+        <v>752864</v>
       </c>
       <c r="R37" t="n">
-        <v>7096096</v>
+        <v>7096134</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4846,7 +4851,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4856,7 +4861,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4883,7 +4893,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120380955</v>
+        <v>120382045</v>
       </c>
       <c r="B38" t="n">
         <v>91858</v>
@@ -4923,13 +4933,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752864</v>
+        <v>752897</v>
       </c>
       <c r="R38" t="n">
-        <v>7096134</v>
+        <v>7096388</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4958,7 +4968,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4968,7 +4978,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4995,10 +5005,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120380082</v>
+        <v>120381406</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5007,41 +5017,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752824</v>
+        <v>752823</v>
       </c>
       <c r="R39" t="n">
-        <v>7096268</v>
+        <v>7096244</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5070,7 +5089,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5080,7 +5099,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5107,7 +5126,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120379894</v>
+        <v>120380070</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -5147,10 +5166,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>752841</v>
+        <v>752828</v>
       </c>
       <c r="R40" t="n">
-        <v>7096393</v>
+        <v>7096259</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5182,7 +5201,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5192,7 +5211,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5219,10 +5238,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120382031</v>
+        <v>120380745</v>
       </c>
       <c r="B41" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5231,25 +5250,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5259,13 +5278,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752880</v>
+        <v>752848</v>
       </c>
       <c r="R41" t="n">
-        <v>7096382</v>
+        <v>7096115</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5294,7 +5313,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5304,7 +5323,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,10 +5350,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120381495</v>
+        <v>120381218</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5343,25 +5362,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5371,10 +5390,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752822</v>
+        <v>752828</v>
       </c>
       <c r="R42" t="n">
-        <v>7096246</v>
+        <v>7096213</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5406,7 +5425,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5416,7 +5435,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5443,10 +5462,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120382019</v>
+        <v>120382173</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5455,25 +5474,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5483,13 +5502,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752883</v>
+        <v>752897</v>
       </c>
       <c r="R43" t="n">
-        <v>7096380</v>
+        <v>7096388</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5518,7 +5537,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5528,7 +5547,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Växte dolt under fallen tallgren</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5555,10 +5579,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120379986</v>
+        <v>120381495</v>
       </c>
       <c r="B44" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5567,25 +5591,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5595,10 +5619,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752810</v>
+        <v>752822</v>
       </c>
       <c r="R44" t="n">
-        <v>7096318</v>
+        <v>7096246</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5630,7 +5654,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5640,7 +5664,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,7 +5691,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120381720</v>
+        <v>120380394</v>
       </c>
       <c r="B45" t="n">
         <v>91858</v>
@@ -5707,13 +5731,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752888</v>
+        <v>752866</v>
       </c>
       <c r="R45" t="n">
-        <v>7096340</v>
+        <v>7096140</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5742,7 +5766,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,7 +5776,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5779,10 +5803,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120381175</v>
+        <v>120382019</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5795,39 +5819,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752840</v>
+        <v>752883</v>
       </c>
       <c r="R46" t="n">
-        <v>7096209</v>
+        <v>7096380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5859,7 +5878,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5869,7 +5888,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5896,10 +5915,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120380429</v>
+        <v>120382031</v>
       </c>
       <c r="B47" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5912,21 +5931,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5936,13 +5955,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752866</v>
+        <v>752880</v>
       </c>
       <c r="R47" t="n">
-        <v>7096140</v>
+        <v>7096382</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5971,7 +5990,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5981,7 +6000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6008,7 +6027,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120380745</v>
+        <v>120379894</v>
       </c>
       <c r="B48" t="n">
         <v>91858</v>
@@ -6048,10 +6067,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752848</v>
+        <v>752841</v>
       </c>
       <c r="R48" t="n">
-        <v>7096115</v>
+        <v>7096393</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6083,7 +6102,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6093,7 +6112,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6120,10 +6139,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120382173</v>
+        <v>120381956</v>
       </c>
       <c r="B49" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6132,25 +6151,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6160,13 +6179,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752897</v>
+        <v>752894</v>
       </c>
       <c r="R49" t="n">
-        <v>7096388</v>
+        <v>7096354</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6195,7 +6214,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6205,12 +6224,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Växte dolt under fallen tallgren</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6237,10 +6251,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120380249</v>
+        <v>120380690</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6249,25 +6263,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6277,10 +6291,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752872</v>
+        <v>752855</v>
       </c>
       <c r="R50" t="n">
-        <v>7096227</v>
+        <v>7096096</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6312,7 +6326,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,7 +6336,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6349,10 +6363,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120381968</v>
+        <v>120380429</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6361,25 +6375,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6389,13 +6403,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>752894</v>
+        <v>752866</v>
       </c>
       <c r="R51" t="n">
-        <v>7096354</v>
+        <v>7096140</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6424,7 +6438,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6448,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120381218</v>
+        <v>120380299</v>
       </c>
       <c r="B52" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6477,21 +6491,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6501,10 +6515,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752828</v>
+        <v>752874</v>
       </c>
       <c r="R52" t="n">
-        <v>7096213</v>
+        <v>7096153</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6536,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6546,7 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6573,10 +6587,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120381406</v>
+        <v>120381039</v>
       </c>
       <c r="B53" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6589,46 +6603,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752823</v>
+        <v>752854</v>
       </c>
       <c r="R53" t="n">
-        <v>7096244</v>
+        <v>7096154</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6657,7 +6662,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6667,7 +6672,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6694,10 +6699,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120380784</v>
+        <v>120380955</v>
       </c>
       <c r="B54" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6706,25 +6711,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6769,7 +6774,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6779,12 +6784,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6811,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120380070</v>
+        <v>120380566</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6823,25 +6823,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752828</v>
+        <v>752866</v>
       </c>
       <c r="R55" t="n">
-        <v>7096259</v>
+        <v>7096140</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -3636,10 +3636,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120379906</v>
+        <v>120380698</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>91852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,39 +3652,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Hissjö, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752841</v>
+        <v>752855</v>
       </c>
       <c r="R27" t="n">
-        <v>7096393</v>
+        <v>7096096</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3716,7 +3711,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3726,7 +3721,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3753,10 +3748,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120379986</v>
+        <v>120379979</v>
       </c>
       <c r="B28" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3765,25 +3760,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752810</v>
+        <v>752829</v>
       </c>
       <c r="R28" t="n">
-        <v>7096318</v>
+        <v>7096331</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3828,7 +3823,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3838,7 +3833,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3865,7 +3860,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120380132</v>
+        <v>120381720</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3905,10 +3900,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752824</v>
+        <v>752888</v>
       </c>
       <c r="R29" t="n">
-        <v>7096268</v>
+        <v>7096340</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3940,7 +3935,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3950,7 +3945,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3977,10 +3972,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120380287</v>
+        <v>120380070</v>
       </c>
       <c r="B30" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3989,25 +3984,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4017,13 +4012,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752880</v>
+        <v>752828</v>
       </c>
       <c r="R30" t="n">
-        <v>7096182</v>
+        <v>7096259</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4052,7 +4047,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4062,7 +4057,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4089,10 +4084,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120380698</v>
+        <v>120380082</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4101,25 +4096,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4129,10 +4124,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752855</v>
+        <v>752824</v>
       </c>
       <c r="R31" t="n">
-        <v>7096096</v>
+        <v>7096268</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4164,7 +4159,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4174,7 +4169,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4201,7 +4196,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120381720</v>
+        <v>120381968</v>
       </c>
       <c r="B32" t="n">
         <v>91858</v>
@@ -4241,13 +4236,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752888</v>
+        <v>752894</v>
       </c>
       <c r="R32" t="n">
-        <v>7096340</v>
+        <v>7096354</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4276,7 +4271,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,7 +4281,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4430,10 +4425,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120380981</v>
+        <v>120379894</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4442,43 +4437,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752849</v>
+        <v>752841</v>
       </c>
       <c r="R34" t="n">
-        <v>7096158</v>
+        <v>7096393</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4510,7 +4500,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4520,12 +4510,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe tunn</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,10 +4537,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120380249</v>
+        <v>120380299</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4564,25 +4549,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4592,10 +4577,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752872</v>
+        <v>752874</v>
       </c>
       <c r="R35" t="n">
-        <v>7096227</v>
+        <v>7096153</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4627,7 +4612,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4637,7 +4622,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4664,10 +4649,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120379979</v>
+        <v>120379986</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4661,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4689,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752829</v>
+        <v>752810</v>
       </c>
       <c r="R36" t="n">
-        <v>7096331</v>
+        <v>7096318</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4739,7 +4724,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4749,7 +4734,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4776,10 +4761,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120380784</v>
+        <v>120381039</v>
       </c>
       <c r="B37" t="n">
-        <v>91862</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4788,25 +4773,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4816,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752864</v>
+        <v>752854</v>
       </c>
       <c r="R37" t="n">
-        <v>7096134</v>
+        <v>7096154</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4851,7 +4836,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4861,12 +4846,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4893,10 +4873,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120382045</v>
+        <v>120382031</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4905,25 +4885,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4933,10 +4913,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752897</v>
+        <v>752880</v>
       </c>
       <c r="R38" t="n">
-        <v>7096388</v>
+        <v>7096382</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4968,7 +4948,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4978,7 +4958,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5005,10 +4985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120381406</v>
+        <v>120382045</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5017,47 +4997,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752823</v>
+        <v>752897</v>
       </c>
       <c r="R39" t="n">
-        <v>7096244</v>
+        <v>7096388</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5089,7 +5060,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5099,7 +5070,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5126,10 +5097,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120380070</v>
+        <v>120381218</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5138,25 +5109,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5169,7 +5140,7 @@
         <v>752828</v>
       </c>
       <c r="R40" t="n">
-        <v>7096259</v>
+        <v>7096213</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5201,7 +5172,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5211,7 +5182,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5238,7 +5209,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120380745</v>
+        <v>120380394</v>
       </c>
       <c r="B41" t="n">
         <v>91858</v>
@@ -5278,13 +5249,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752848</v>
+        <v>752866</v>
       </c>
       <c r="R41" t="n">
-        <v>7096115</v>
+        <v>7096140</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5313,7 +5284,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5323,7 +5294,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5350,10 +5321,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120381218</v>
+        <v>120380249</v>
       </c>
       <c r="B42" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5362,25 +5333,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5390,10 +5361,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752828</v>
+        <v>752872</v>
       </c>
       <c r="R42" t="n">
-        <v>7096213</v>
+        <v>7096227</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5425,7 +5396,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5435,7 +5406,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5462,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120382173</v>
+        <v>120379906</v>
       </c>
       <c r="B43" t="n">
-        <v>91901</v>
+        <v>57336</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5478,34 +5449,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752897</v>
+        <v>752841</v>
       </c>
       <c r="R43" t="n">
-        <v>7096388</v>
+        <v>7096393</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5537,7 +5513,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5547,12 +5523,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växte dolt under fallen tallgren</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5579,10 +5550,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120381495</v>
+        <v>120382173</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5591,25 +5562,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5619,10 +5590,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752822</v>
+        <v>752897</v>
       </c>
       <c r="R44" t="n">
-        <v>7096246</v>
+        <v>7096388</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5654,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5664,7 +5635,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växte dolt under fallen tallgren</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5691,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120380394</v>
+        <v>120380690</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5703,25 +5679,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5731,13 +5707,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752866</v>
+        <v>752855</v>
       </c>
       <c r="R45" t="n">
-        <v>7096140</v>
+        <v>7096096</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5766,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5776,7 +5752,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5803,10 +5779,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120382019</v>
+        <v>120380981</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5815,41 +5791,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752883</v>
+        <v>752849</v>
       </c>
       <c r="R46" t="n">
-        <v>7096380</v>
+        <v>7096158</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5878,7 +5859,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5888,7 +5869,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe tunn</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5915,10 +5901,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120382031</v>
+        <v>120381406</v>
       </c>
       <c r="B47" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5931,34 +5917,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752880</v>
+        <v>752823</v>
       </c>
       <c r="R47" t="n">
-        <v>7096382</v>
+        <v>7096244</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5990,7 +5985,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6000,7 +5995,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6027,10 +6022,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120379894</v>
+        <v>120380287</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6039,25 +6034,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6067,13 +6062,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752841</v>
+        <v>752880</v>
       </c>
       <c r="R48" t="n">
-        <v>7096393</v>
+        <v>7096182</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6102,7 +6097,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6112,7 +6107,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6139,10 +6134,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120381956</v>
+        <v>120380784</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6151,25 +6146,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6179,13 +6174,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752894</v>
+        <v>752864</v>
       </c>
       <c r="R49" t="n">
-        <v>7096354</v>
+        <v>7096134</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6214,7 +6209,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6224,7 +6219,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6251,10 +6251,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120380690</v>
+        <v>120380745</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6263,25 +6263,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752855</v>
+        <v>752848</v>
       </c>
       <c r="R50" t="n">
-        <v>7096096</v>
+        <v>7096115</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6475,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120380299</v>
+        <v>120381495</v>
       </c>
       <c r="B52" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6487,25 +6487,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752874</v>
+        <v>752822</v>
       </c>
       <c r="R52" t="n">
-        <v>7096153</v>
+        <v>7096246</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6587,10 +6587,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120381039</v>
+        <v>120382019</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6599,25 +6599,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752854</v>
+        <v>752883</v>
       </c>
       <c r="R53" t="n">
-        <v>7096154</v>
+        <v>7096380</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6699,10 +6699,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120380955</v>
+        <v>120380566</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6711,25 +6711,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752864</v>
+        <v>752866</v>
       </c>
       <c r="R54" t="n">
-        <v>7096134</v>
+        <v>7096140</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6811,10 +6811,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120380566</v>
+        <v>120380955</v>
       </c>
       <c r="B55" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6823,25 +6823,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752866</v>
+        <v>752864</v>
       </c>
       <c r="R55" t="n">
-        <v>7096140</v>
+        <v>7096134</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 17522-2022 artfynd.xlsx
+++ b/artfynd/A 17522-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,7 +2166,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102942267</v>
+        <v>102942281</v>
       </c>
       <c r="B14" t="n">
         <v>90653</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752870.1470578411</v>
+        <v>752798.5705554254</v>
       </c>
       <c r="R14" t="n">
-        <v>7096198.166440388</v>
+        <v>7096393.099418482</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102942281</v>
+        <v>102942271</v>
       </c>
       <c r="B15" t="n">
         <v>90653</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752798.5705554254</v>
+        <v>752867.1291650967</v>
       </c>
       <c r="R15" t="n">
-        <v>7096393.099418482</v>
+        <v>7096208.091471967</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102942271</v>
+        <v>102942277</v>
       </c>
       <c r="B16" t="n">
         <v>90653</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752867.1291650967</v>
+        <v>752841.3089346009</v>
       </c>
       <c r="R16" t="n">
-        <v>7096208.091471967</v>
+        <v>7096351.906918597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102942277</v>
+        <v>102942264</v>
       </c>
       <c r="B17" t="n">
         <v>90653</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752841.3089346009</v>
+        <v>752838.0645236919</v>
       </c>
       <c r="R17" t="n">
-        <v>7096351.906918597</v>
+        <v>7096282.670394217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102942264</v>
+        <v>102942274</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
+        <v>77532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2686,31 +2686,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752838.0645236919</v>
+        <v>752842.4808325218</v>
       </c>
       <c r="R18" t="n">
-        <v>7096282.670394217</v>
+        <v>7096321.052343457</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102942274</v>
+        <v>119718993</v>
       </c>
       <c r="B19" t="n">
-        <v>77532</v>
+        <v>91902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2808,47 +2808,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Piparböle naturvårdsområde, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752842.4808325218</v>
+        <v>752872</v>
       </c>
       <c r="R19" t="n">
-        <v>7096321.052343457</v>
+        <v>7096313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2875,22 +2866,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2901,31 +2882,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Andreas Estensen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Tonje Lindmark</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119718993</v>
+        <v>119719025</v>
       </c>
       <c r="B20" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2934,25 +2910,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2962,10 +2938,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752872</v>
+        <v>752861</v>
       </c>
       <c r="R20" t="n">
-        <v>7096313</v>
+        <v>7096410</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,7 +3000,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119719025</v>
+        <v>119719029</v>
       </c>
       <c r="B21" t="n">
         <v>91858</v>
@@ -3064,10 +3040,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752861</v>
+        <v>752841</v>
       </c>
       <c r="R21" t="n">
-        <v>7096410</v>
+        <v>7096319</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3102,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119719029</v>
+        <v>119719028</v>
       </c>
       <c r="B22" t="n">
         <v>91858</v>
@@ -3166,10 +3142,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752841</v>
+        <v>752873</v>
       </c>
       <c r="R22" t="n">
-        <v>7096319</v>
+        <v>7096242</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3228,7 +3204,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119719028</v>
+        <v>119719027</v>
       </c>
       <c r="B23" t="n">
         <v>91858</v>
@@ -3268,10 +3244,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752873</v>
+        <v>752872</v>
       </c>
       <c r="R23" t="n">
-        <v>7096242</v>
+        <v>7096313</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3330,10 +3306,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119719027</v>
+        <v>119718989</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3342,25 +3318,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3370,10 +3346,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752872</v>
+        <v>752861</v>
       </c>
       <c r="R24" t="n">
-        <v>7096313</v>
+        <v>7096410</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3432,10 +3408,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119718989</v>
+        <v>119719023</v>
       </c>
       <c r="B25" t="n">
-        <v>89292</v>
+        <v>89269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3448,21 +3424,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3448,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>752861</v>
+        <v>752859</v>
       </c>
       <c r="R25" t="n">
-        <v>7096410</v>
+        <v>7096271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,10 +3510,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119719023</v>
+        <v>120380249</v>
       </c>
       <c r="B26" t="n">
-        <v>89269</v>
+        <v>91913</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3546,41 +3522,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752859</v>
+        <v>752872</v>
       </c>
       <c r="R26" t="n">
-        <v>7096271</v>
+        <v>7096227</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3604,12 +3580,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3624,19 +3610,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120380249</v>
+        <v>120381956</v>
       </c>
       <c r="B27" t="n">
         <v>91913</v>
@@ -3676,13 +3662,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752872</v>
+        <v>752894</v>
       </c>
       <c r="R27" t="n">
-        <v>7096227</v>
+        <v>7096354</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3711,7 +3697,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3721,7 +3707,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,7 +3734,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120381956</v>
+        <v>120382086</v>
       </c>
       <c r="B28" t="n">
         <v>91913</v>
@@ -3788,10 +3774,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752894</v>
+        <v>752897</v>
       </c>
       <c r="R28" t="n">
-        <v>7096354</v>
+        <v>7096388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3809,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,7 +3819,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,7 +3846,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120382086</v>
+        <v>120380394</v>
       </c>
       <c r="B29" t="n">
         <v>91913</v>
@@ -3900,10 +3886,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752897</v>
+        <v>752866</v>
       </c>
       <c r="R29" t="n">
-        <v>7096388</v>
+        <v>7096140</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3935,7 +3921,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3945,7 +3931,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,10 +3958,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120380394</v>
+        <v>120381218</v>
       </c>
       <c r="B30" t="n">
-        <v>91913</v>
+        <v>91905</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3984,25 +3970,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4012,13 +3998,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752866</v>
+        <v>752828</v>
       </c>
       <c r="R30" t="n">
-        <v>7096140</v>
+        <v>7096213</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4047,7 +4033,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,7 +4043,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4084,10 +4070,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120381218</v>
+        <v>120380070</v>
       </c>
       <c r="B31" t="n">
-        <v>91905</v>
+        <v>91913</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4096,25 +4082,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4127,7 +4113,7 @@
         <v>752828</v>
       </c>
       <c r="R31" t="n">
-        <v>7096213</v>
+        <v>7096259</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4159,7 +4145,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4169,7 +4155,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4196,7 +4182,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120380070</v>
+        <v>120379979</v>
       </c>
       <c r="B32" t="n">
         <v>91913</v>
@@ -4236,10 +4222,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752828</v>
+        <v>752829</v>
       </c>
       <c r="R32" t="n">
-        <v>7096259</v>
+        <v>7096331</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4271,7 +4257,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4281,7 +4267,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,10 +4294,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120379979</v>
+        <v>120380299</v>
       </c>
       <c r="B33" t="n">
-        <v>91913</v>
+        <v>91907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4320,25 +4306,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4348,10 +4334,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752829</v>
+        <v>752874</v>
       </c>
       <c r="R33" t="n">
-        <v>7096331</v>
+        <v>7096153</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4383,7 +4369,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4393,7 +4379,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4420,10 +4406,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120380299</v>
+        <v>120380745</v>
       </c>
       <c r="B34" t="n">
-        <v>91907</v>
+        <v>91913</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4432,25 +4418,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4460,10 +4446,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752874</v>
+        <v>752848</v>
       </c>
       <c r="R34" t="n">
-        <v>7096153</v>
+        <v>7096115</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4495,7 +4481,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4505,7 +4491,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4532,10 +4518,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120380745</v>
+        <v>120381039</v>
       </c>
       <c r="B35" t="n">
-        <v>91913</v>
+        <v>91907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4544,25 +4530,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4572,10 +4558,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752848</v>
+        <v>752854</v>
       </c>
       <c r="R35" t="n">
-        <v>7096115</v>
+        <v>7096154</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4607,7 +4593,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4617,7 +4603,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4644,7 +4630,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120381039</v>
+        <v>120380698</v>
       </c>
       <c r="B36" t="n">
         <v>91907</v>
@@ -4684,10 +4670,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752854</v>
+        <v>752855</v>
       </c>
       <c r="R36" t="n">
-        <v>7096154</v>
+        <v>7096096</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4719,7 +4705,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4729,7 +4715,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4756,10 +4742,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120380698</v>
+        <v>120381495</v>
       </c>
       <c r="B37" t="n">
-        <v>91907</v>
+        <v>91913</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4768,25 +4754,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4796,10 +4782,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752855</v>
+        <v>752822</v>
       </c>
       <c r="R37" t="n">
-        <v>7096096</v>
+        <v>7096246</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4831,7 +4817,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4841,7 +4827,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4868,7 +4854,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120381495</v>
+        <v>120381720</v>
       </c>
       <c r="B38" t="n">
         <v>91913</v>
@@ -4908,10 +4894,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752822</v>
+        <v>752888</v>
       </c>
       <c r="R38" t="n">
-        <v>7096246</v>
+        <v>7096340</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4943,7 +4929,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4953,7 +4939,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4980,10 +4966,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120381720</v>
+        <v>120379906</v>
       </c>
       <c r="B39" t="n">
-        <v>91913</v>
+        <v>57351</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4992,38 +4978,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
+          <t>Piparböle naturreservat, Hissjö, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752888</v>
+        <v>752841</v>
       </c>
       <c r="R39" t="n">
-        <v>7096340</v>
+        <v>7096393</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5055,7 +5046,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,7 +5056,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,10 +5083,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120379906</v>
+        <v>120381175</v>
       </c>
       <c r="B40" t="n">
-        <v>57351</v>
+        <v>57704</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5104,20 +5095,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5128,22 +5119,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Piparböle naturreservat, Hissjö, Vb</t>
+          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>752841</v>
+        <v>752840</v>
       </c>
       <c r="R40" t="n">
-        <v>7096393</v>
+        <v>7096209</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5172,7 +5163,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5182,7 +5173,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5209,10 +5200,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120381175</v>
+        <v>120379986</v>
       </c>
       <c r="B41" t="n">
-        <v>57704</v>
+        <v>91929</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5221,46 +5212,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752840</v>
+        <v>752810</v>
       </c>
       <c r="R41" t="n">
-        <v>7096209</v>
+        <v>7096318</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5289,7 +5275,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5299,7 +5285,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5326,10 +5312,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120379986</v>
+        <v>120382019</v>
       </c>
       <c r="B42" t="n">
-        <v>91929</v>
+        <v>91913</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5338,25 +5324,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5366,13 +5352,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752810</v>
+        <v>752883</v>
       </c>
       <c r="R42" t="n">
-        <v>7096318</v>
+        <v>7096380</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5401,7 +5387,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5411,7 +5397,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5438,10 +5424,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120382019</v>
+        <v>120380287</v>
       </c>
       <c r="B43" t="n">
-        <v>91913</v>
+        <v>91905</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5450,25 +5436,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5478,10 +5464,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752883</v>
+        <v>752880</v>
       </c>
       <c r="R43" t="n">
-        <v>7096380</v>
+        <v>7096182</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5513,7 +5499,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5523,7 +5509,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5550,10 +5536,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120380287</v>
+        <v>120380955</v>
       </c>
       <c r="B44" t="n">
-        <v>91905</v>
+        <v>91913</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5562,25 +5548,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5590,13 +5576,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752880</v>
+        <v>752864</v>
       </c>
       <c r="R44" t="n">
-        <v>7096182</v>
+        <v>7096134</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5625,7 +5611,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,7 +5621,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5662,10 +5648,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120380955</v>
+        <v>120380429</v>
       </c>
       <c r="B45" t="n">
-        <v>91913</v>
+        <v>91907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5674,25 +5660,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5702,10 +5688,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>752864</v>
+        <v>752866</v>
       </c>
       <c r="R45" t="n">
-        <v>7096134</v>
+        <v>7096140</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5737,7 +5723,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5747,7 +5733,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5774,10 +5760,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120380429</v>
+        <v>120380566</v>
       </c>
       <c r="B46" t="n">
-        <v>91907</v>
+        <v>91948</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5790,21 +5776,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5849,7 +5835,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5859,7 +5845,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5886,10 +5872,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120380566</v>
+        <v>120382173</v>
       </c>
       <c r="B47" t="n">
-        <v>91948</v>
+        <v>91939</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5902,21 +5888,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5926,10 +5912,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752866</v>
+        <v>752897</v>
       </c>
       <c r="R47" t="n">
-        <v>7096140</v>
+        <v>7096388</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5961,7 +5947,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5971,7 +5957,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växte dolt under fallen tallgren</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5998,10 +5989,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120382173</v>
+        <v>120380981</v>
       </c>
       <c r="B48" t="n">
-        <v>91939</v>
+        <v>57351</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6014,34 +6005,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752897</v>
+        <v>752849</v>
       </c>
       <c r="R48" t="n">
-        <v>7096388</v>
+        <v>7096158</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6073,7 +6069,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6083,12 +6079,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Växte dolt under fallen tallgren</t>
+          <t>Tallhögstubbe tunn</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6115,10 +6111,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120380981</v>
+        <v>120380132</v>
       </c>
       <c r="B49" t="n">
-        <v>57351</v>
+        <v>91913</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6127,43 +6123,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752849</v>
+        <v>752824</v>
       </c>
       <c r="R49" t="n">
-        <v>7096158</v>
+        <v>7096268</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6195,7 +6186,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6205,12 +6196,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe tunn</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6237,10 +6223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120380132</v>
+        <v>120380784</v>
       </c>
       <c r="B50" t="n">
-        <v>91913</v>
+        <v>91917</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6249,25 +6235,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6277,10 +6263,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752824</v>
+        <v>752864</v>
       </c>
       <c r="R50" t="n">
-        <v>7096268</v>
+        <v>7096134</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6312,7 +6298,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,7 +6308,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6349,10 +6340,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120380784</v>
+        <v>120379894</v>
       </c>
       <c r="B51" t="n">
-        <v>91917</v>
+        <v>91913</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6361,25 +6352,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6389,10 +6380,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>752864</v>
+        <v>752841</v>
       </c>
       <c r="R51" t="n">
-        <v>7096134</v>
+        <v>7096393</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6424,7 +6415,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,12 +6425,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, nyare, knäckt med bark kvar</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6466,10 +6452,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120379894</v>
+        <v>120382031</v>
       </c>
       <c r="B52" t="n">
-        <v>91913</v>
+        <v>91929</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6478,25 +6464,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6506,13 +6492,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752841</v>
+        <v>752880</v>
       </c>
       <c r="R52" t="n">
-        <v>7096393</v>
+        <v>7096382</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6541,7 +6527,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6551,7 +6537,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6578,10 +6564,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120382031</v>
+        <v>120380690</v>
       </c>
       <c r="B53" t="n">
-        <v>91929</v>
+        <v>78564</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6594,21 +6580,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6618,13 +6604,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752880</v>
+        <v>752855</v>
       </c>
       <c r="R53" t="n">
-        <v>7096382</v>
+        <v>7096096</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6653,7 +6639,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6663,7 +6649,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6690,10 +6676,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120380690</v>
+        <v>120381406</v>
       </c>
       <c r="B54" t="n">
-        <v>78564</v>
+        <v>91905</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6706,37 +6692,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752855</v>
+        <v>752823</v>
       </c>
       <c r="R54" t="n">
-        <v>7096096</v>
+        <v>7096244</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6765,7 +6760,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6775,7 +6770,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6799,127 +6794,6 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>120381406</v>
-      </c>
-      <c r="B55" t="n">
-        <v>91905</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Piparböle naturreservat, Piparböle naturreservat, Vb</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>752823</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7096244</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
